--- a/artfynd/A 42861-2025 artfynd.xlsx
+++ b/artfynd/A 42861-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128340143</v>
       </c>
       <c r="B2" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128339889</v>
       </c>
       <c r="B3" t="n">
-        <v>92639</v>
+        <v>92644</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42861-2025 artfynd.xlsx
+++ b/artfynd/A 42861-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128340143</v>
       </c>
       <c r="B2" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128339889</v>
       </c>
       <c r="B3" t="n">
-        <v>92644</v>
+        <v>92736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42861-2025 artfynd.xlsx
+++ b/artfynd/A 42861-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128340143</v>
       </c>
       <c r="B2" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128339889</v>
       </c>
       <c r="B3" t="n">
-        <v>92736</v>
+        <v>92748</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42861-2025 artfynd.xlsx
+++ b/artfynd/A 42861-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128340143</v>
       </c>
       <c r="B2" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128339889</v>
       </c>
       <c r="B3" t="n">
-        <v>92748</v>
+        <v>92750</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42861-2025 artfynd.xlsx
+++ b/artfynd/A 42861-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128340143</v>
       </c>
       <c r="B2" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128339889</v>
       </c>
       <c r="B3" t="n">
-        <v>92750</v>
+        <v>92751</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42861-2025 artfynd.xlsx
+++ b/artfynd/A 42861-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128340143</v>
       </c>
       <c r="B2" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128339889</v>
       </c>
       <c r="B3" t="n">
-        <v>92751</v>
+        <v>92778</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42861-2025 artfynd.xlsx
+++ b/artfynd/A 42861-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128340143</v>
       </c>
       <c r="B2" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128339889</v>
       </c>
       <c r="B3" t="n">
-        <v>92778</v>
+        <v>92788</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42861-2025 artfynd.xlsx
+++ b/artfynd/A 42861-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128340143</v>
       </c>
       <c r="B2" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128339889</v>
       </c>
       <c r="B3" t="n">
-        <v>92788</v>
+        <v>92792</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42861-2025 artfynd.xlsx
+++ b/artfynd/A 42861-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128340143</v>
+        <v>128339889</v>
       </c>
       <c r="B2" t="n">
-        <v>92798</v>
+        <v>93191</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>826899</v>
+        <v>827015</v>
       </c>
       <c r="R2" t="n">
-        <v>7397619</v>
+        <v>7397667</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -744,12 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128339889</v>
+        <v>128340143</v>
       </c>
       <c r="B3" t="n">
-        <v>92792</v>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>827015</v>
+        <v>826899</v>
       </c>
       <c r="R3" t="n">
-        <v>7397667</v>
+        <v>7397619</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,12 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -884,6 +884,112 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128340142</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Naisjärv, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>826962</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7397590</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42861-2025 artfynd.xlsx
+++ b/artfynd/A 42861-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128339889</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340143</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,8 +1005,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340142</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>